--- a/materials/introduction_with_solutions.xlsx
+++ b/materials/introduction_with_solutions.xlsx
@@ -1,155 +1,122 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\Lehre\Introduction to Programming\Presentation\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A67147D8-0527-4183-ADD1-4ED59F0E6DFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="90" yWindow="75" windowWidth="12000" windowHeight="7245"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="22365" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Anfang" sheetId="4" r:id="rId1"/>
-    <sheet name="Maske" sheetId="7" r:id="rId2"/>
-    <sheet name="mit Graphik" sheetId="1" r:id="rId3"/>
-    <sheet name="Einfach" sheetId="6" r:id="rId4"/>
-    <sheet name="Wenn" sheetId="5" r:id="rId5"/>
-    <sheet name="Solver" sheetId="8" r:id="rId6"/>
+    <sheet name="Start" sheetId="4" r:id="rId1"/>
+    <sheet name="Cost_Revenue" sheetId="7" r:id="rId2"/>
+    <sheet name="with_plot" sheetId="1" r:id="rId3"/>
+    <sheet name="simple" sheetId="6" r:id="rId4"/>
+    <sheet name="conditional_cost" sheetId="5" r:id="rId5"/>
   </sheets>
-  <definedNames>
-    <definedName name="solver_adj" localSheetId="5" hidden="1">Solver!$B$4</definedName>
-    <definedName name="solver_cvg" localSheetId="5" hidden="1">0.001</definedName>
-    <definedName name="solver_drv" localSheetId="5" hidden="1">1</definedName>
-    <definedName name="solver_eng" localSheetId="5" hidden="1">1</definedName>
-    <definedName name="solver_est" localSheetId="5" hidden="1">1</definedName>
-    <definedName name="solver_itr" localSheetId="5" hidden="1">100</definedName>
-    <definedName name="solver_lin" localSheetId="5" hidden="1">2</definedName>
-    <definedName name="solver_neg" localSheetId="5" hidden="1">2</definedName>
-    <definedName name="solver_num" localSheetId="5" hidden="1">0</definedName>
-    <definedName name="solver_nwt" localSheetId="5" hidden="1">1</definedName>
-    <definedName name="solver_opt" localSheetId="5" hidden="1">Solver!$B$5</definedName>
-    <definedName name="solver_pre" localSheetId="5" hidden="1">0.000001</definedName>
-    <definedName name="solver_scl" localSheetId="5" hidden="1">2</definedName>
-    <definedName name="solver_sho" localSheetId="5" hidden="1">2</definedName>
-    <definedName name="solver_tim" localSheetId="5" hidden="1">100</definedName>
-    <definedName name="solver_tol" localSheetId="5" hidden="1">0.05</definedName>
-    <definedName name="solver_typ" localSheetId="5" hidden="1">2</definedName>
-    <definedName name="solver_val" localSheetId="5" hidden="1">0</definedName>
-    <definedName name="solver_ver" localSheetId="5" hidden="1">3</definedName>
-  </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="33">
-  <si>
-    <t>Erlöse</t>
-  </si>
-  <si>
-    <t>Kosten- und Erlösrechnung</t>
-  </si>
-  <si>
-    <t>Fixkosten (Jahr) =</t>
-  </si>
-  <si>
-    <t>var. Kosten (Stück) =</t>
-  </si>
-  <si>
-    <t>Preis (Stück) =</t>
-  </si>
-  <si>
-    <t>Monat</t>
-  </si>
-  <si>
-    <t>Januar</t>
-  </si>
-  <si>
-    <t>Februar</t>
-  </si>
-  <si>
-    <t>März</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="29">
   <si>
     <t>April</t>
   </si>
   <si>
-    <t>Mai</t>
-  </si>
-  <si>
-    <t>Juni</t>
-  </si>
-  <si>
-    <t>Juli</t>
-  </si>
-  <si>
     <t>August</t>
   </si>
   <si>
     <t>September</t>
   </si>
   <si>
-    <t>Oktober</t>
-  </si>
-  <si>
     <t>November</t>
   </si>
   <si>
-    <t>Dezember</t>
-  </si>
-  <si>
-    <t>Gesamt</t>
-  </si>
-  <si>
-    <t>Erlös (Stück) =</t>
-  </si>
-  <si>
-    <t>Gewinn (Jahr) =</t>
-  </si>
-  <si>
-    <t>Fixkosten (Jahr):</t>
-  </si>
-  <si>
-    <t>Gesamt &lt; 130000 =</t>
-  </si>
-  <si>
-    <t>Gesamt &gt;= 130000 =</t>
-  </si>
-  <si>
-    <t>Produktion</t>
-  </si>
-  <si>
-    <t>Verschiebung x</t>
-  </si>
-  <si>
-    <t>Verschiebung y</t>
-  </si>
-  <si>
-    <t>Gleichung</t>
-  </si>
-  <si>
-    <t>X-Wert</t>
-  </si>
-  <si>
-    <t>Zahl 1</t>
-  </si>
-  <si>
-    <t>Zahl 2</t>
-  </si>
-  <si>
     <t>Addition</t>
   </si>
   <si>
-    <t>Hoch</t>
+    <t>Cost and revenue calculation</t>
+  </si>
+  <si>
+    <t>Number 1</t>
+  </si>
+  <si>
+    <t>Number 2</t>
+  </si>
+  <si>
+    <t>Exponent</t>
+  </si>
+  <si>
+    <t>Month</t>
+  </si>
+  <si>
+    <t>January</t>
+  </si>
+  <si>
+    <t>February</t>
+  </si>
+  <si>
+    <t>March</t>
+  </si>
+  <si>
+    <t>May</t>
+  </si>
+  <si>
+    <t>June</t>
+  </si>
+  <si>
+    <t>July</t>
+  </si>
+  <si>
+    <t>October</t>
+  </si>
+  <si>
+    <t>December</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Production</t>
+  </si>
+  <si>
+    <t>Revenue</t>
+  </si>
+  <si>
+    <t>Price (per unit) =</t>
+  </si>
+  <si>
+    <t>var. Cost (per unit) =</t>
+  </si>
+  <si>
+    <t>Revenue (per unti) =</t>
+  </si>
+  <si>
+    <t>Fixed cost (per year) =</t>
+  </si>
+  <si>
+    <t>Profit (per year) =</t>
+  </si>
+  <si>
+    <t>Fixed cost (per year):</t>
+  </si>
+  <si>
+    <t>Production &lt; 130000 =</t>
+  </si>
+  <si>
+    <t>Production &gt;= 130000 =</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -205,7 +172,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -218,7 +185,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -231,7 +197,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -249,7 +215,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="de-DE"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -327,11 +293,11 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'mit Graphik'!$B$3</c:f>
+              <c:f>with_plot!$B$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Produktion</c:v>
+                  <c:v>Production</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -350,29 +316,29 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'mit Graphik'!$A$4:$A$15</c:f>
+              <c:f>with_plot!$A$4:$A$15</c:f>
               <c:strCache>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>Januar</c:v>
+                  <c:v>January</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Februar</c:v>
+                  <c:v>February</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>März</c:v>
+                  <c:v>March</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>April</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>Mai</c:v>
+                  <c:v>May</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>Juni</c:v>
+                  <c:v>June</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>Juli</c:v>
+                  <c:v>July</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>August</c:v>
@@ -381,20 +347,20 @@
                   <c:v>September</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>Oktober</c:v>
+                  <c:v>October</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>November</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>Dezember</c:v>
+                  <c:v>December</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'mit Graphik'!$B$4:$B$15</c:f>
+              <c:f>with_plot!$B$4:$B$15</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
@@ -599,378 +565,6 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="de-DE"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout>
-        <c:manualLayout>
-          <c:layoutTarget val="inner"/>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="9.775967413441955E-2"/>
-          <c:y val="8.6092715231788075E-2"/>
-          <c:w val="0.85539714867617112"/>
-          <c:h val="0.76490066225165565"/>
-        </c:manualLayout>
-      </c:layout>
-      <c:scatterChart>
-        <c:scatterStyle val="lineMarker"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:spPr>
-            <a:ln w="12700">
-              <a:solidFill>
-                <a:srgbClr val="000080"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>Solver!$D$3:$D$27</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>7</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>11</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>13</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>14</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>15</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>16</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>17</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>18</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>19</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>20</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>21</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>22</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>23</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>24</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>25</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Solver!$E$3:$E$27</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
-                <c:pt idx="0">
-                  <c:v>126</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>105</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>86</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>69</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>54</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>41</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>30</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>21</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>14</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>14</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>21</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>30</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>41</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>54</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>69</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>86</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>105</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>126</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>149</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>174</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-2A1C-4B67-BAB1-162E8C2581B6}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:axId val="454221712"/>
-        <c:axId val="1"/>
-      </c:scatterChart>
-      <c:valAx>
-        <c:axId val="454221712"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="out"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:ln w="3175">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-          </a:ln>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="0" vert="horz"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Arial"/>
-                <a:ea typeface="Arial"/>
-                <a:cs typeface="Arial"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="de-DE"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:valAx>
-        <c:axId val="1"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="3175">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="out"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:ln w="3175">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-          </a:ln>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="0" vert="horz"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Arial"/>
-                <a:ea typeface="Arial"/>
-                <a:cs typeface="Arial"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="de-DE"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="454221712"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:spPr>
-        <a:solidFill>
-          <a:srgbClr val="C0C0C0"/>
-        </a:solidFill>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="808080"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:srgbClr val="FFFFFF"/>
-    </a:solidFill>
-    <a:ln w="3175">
-      <a:solidFill>
-        <a:srgbClr val="000000"/>
-      </a:solidFill>
-      <a:prstDash val="solid"/>
-    </a:ln>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" baseline="0">
-          <a:solidFill>
-            <a:srgbClr val="000000"/>
-          </a:solidFill>
-          <a:latin typeface="Arial"/>
-          <a:ea typeface="Arial"/>
-          <a:cs typeface="Arial"/>
-        </a:defRPr>
-      </a:pPr>
-      <a:endParaRPr lang="de-DE"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter alignWithMargins="0"/>
-    <c:pageMargins b="0.984251969" l="0.78740157499999996" r="0.78740157499999996" t="0.984251969" header="0.4921259845" footer="0.4921259845"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
@@ -988,44 +582,13 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="1026" name="Diagramm 2"/>
-        <xdr:cNvGraphicFramePr>
-          <a:graphicFrameLocks/>
-        </xdr:cNvGraphicFramePr>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>200025</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>85725</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2049" name="Diagramm 1"/>
+        <xdr:cNvPr id="1026" name="Diagramm 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002040000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr>
           <a:graphicFrameLocks/>
         </xdr:cNvGraphicFramePr>
@@ -1392,29 +955,29 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1" s="8" t="s">
-        <v>29</v>
+      <c r="A1" s="7" t="s">
+        <v>6</v>
       </c>
       <c r="B1">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2" s="8" t="s">
-        <v>30</v>
+      <c r="A2" s="7" t="s">
+        <v>7</v>
       </c>
       <c r="B2">
         <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A3" s="8" t="s">
-        <v>31</v>
+      <c r="A3" s="7" t="s">
+        <v>4</v>
       </c>
       <c r="B3">
         <f>B1+B2</f>
@@ -1422,8 +985,8 @@
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A4" s="8" t="s">
-        <v>32</v>
+      <c r="A4" s="7" t="s">
+        <v>8</v>
       </c>
       <c r="B4">
         <f>B1^B2</f>
@@ -1437,34 +1000,34 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E16"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="4" max="4" width="18.42578125" customWidth="1"/>
+    <col min="4" max="4" width="22.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
+      <c r="A1" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E3">
         <v>20</v>
@@ -1472,13 +1035,13 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B4">
         <v>10000</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="E4">
         <v>18</v>
@@ -1486,13 +1049,13 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B5">
         <v>12000</v>
       </c>
-      <c r="D5" s="7" t="s">
-        <v>19</v>
+      <c r="D5" s="6" t="s">
+        <v>23</v>
       </c>
       <c r="E5" s="3">
         <f>E3-E4</f>
@@ -1501,7 +1064,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B6">
         <v>13000</v>
@@ -1509,13 +1072,13 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="B7">
         <v>9000</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="E7">
         <v>250000</v>
@@ -1523,7 +1086,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B8">
         <v>8000</v>
@@ -1531,7 +1094,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B9">
         <v>11000</v>
@@ -1539,24 +1102,24 @@
       <c r="D9" s="5"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A10" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10" s="6">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10">
         <v>12000</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A11" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" s="6">
+      <c r="A11" t="s">
+        <v>1</v>
+      </c>
+      <c r="B11">
         <v>15000</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B12">
         <v>13000</v>
@@ -1564,7 +1127,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B13">
         <v>11000</v>
@@ -1572,7 +1135,7 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="B14">
         <v>9000</v>
@@ -1599,9 +1162,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F16"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.140625" customWidth="1"/>
     <col min="3" max="3" width="10.28515625" customWidth="1"/>
@@ -1609,27 +1172,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
+      <c r="A1" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
       <c r="F1" s="4"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E3">
         <v>20</v>
@@ -1637,7 +1200,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B4">
         <v>10000</v>
@@ -1647,7 +1210,7 @@
         <v>20000</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="E4">
         <v>18</v>
@@ -1655,7 +1218,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B5">
         <v>12000</v>
@@ -1664,8 +1227,8 @@
         <f t="shared" ref="C5:C15" si="0">B5*$E$5</f>
         <v>24000</v>
       </c>
-      <c r="D5" s="7" t="s">
-        <v>19</v>
+      <c r="D5" s="6" t="s">
+        <v>23</v>
       </c>
       <c r="E5" s="3">
         <f>E3-E4</f>
@@ -1674,7 +1237,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B6">
         <v>13000</v>
@@ -1686,7 +1249,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="B7">
         <v>9000</v>
@@ -1695,8 +1258,8 @@
         <f t="shared" si="0"/>
         <v>18000</v>
       </c>
-      <c r="D7" s="4" t="s">
-        <v>21</v>
+      <c r="D7" s="5" t="s">
+        <v>24</v>
       </c>
       <c r="E7">
         <v>250000</v>
@@ -1704,7 +1267,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B8">
         <v>8000</v>
@@ -1716,7 +1279,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B9">
         <v>11000</v>
@@ -1728,10 +1291,10 @@
       <c r="D9" s="5"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A10" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10" s="6">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10">
         <v>12000</v>
       </c>
       <c r="C10">
@@ -1740,10 +1303,10 @@
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A11" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" s="6">
+      <c r="A11" t="s">
+        <v>1</v>
+      </c>
+      <c r="B11">
         <v>15000</v>
       </c>
       <c r="C11">
@@ -1753,7 +1316,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B12">
         <v>13000</v>
@@ -1765,7 +1328,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B13">
         <v>11000</v>
@@ -1777,7 +1340,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="B14">
         <v>9000</v>
@@ -1814,35 +1377,35 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:E16"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="13" customWidth="1"/>
     <col min="4" max="4" width="22.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
+      <c r="A1" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E3">
         <v>20</v>
@@ -1850,7 +1413,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B4">
         <v>10000</v>
@@ -1860,7 +1423,7 @@
         <v>20000</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="E4">
         <v>18</v>
@@ -1868,7 +1431,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B5">
         <v>12000</v>
@@ -1877,8 +1440,8 @@
         <f t="shared" ref="C5:C15" si="0">B5*$E$5</f>
         <v>24000</v>
       </c>
-      <c r="D5" s="7" t="s">
-        <v>19</v>
+      <c r="D5" s="6" t="s">
+        <v>23</v>
       </c>
       <c r="E5" s="3">
         <f>E3-E4</f>
@@ -1887,7 +1450,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B6">
         <v>13000</v>
@@ -1899,7 +1462,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="B7">
         <v>9000</v>
@@ -1909,7 +1472,7 @@
         <v>18000</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="E7">
         <v>250000</v>
@@ -1917,7 +1480,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B8">
         <v>8000</v>
@@ -1929,7 +1492,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B9">
         <v>11000</v>
@@ -1939,7 +1502,7 @@
         <v>22000</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E9">
         <f>C16-E7</f>
@@ -1947,10 +1510,10 @@
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A10" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10" s="6">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10">
         <v>12000</v>
       </c>
       <c r="C10">
@@ -1959,10 +1522,10 @@
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A11" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" s="6">
+      <c r="A11" t="s">
+        <v>1</v>
+      </c>
+      <c r="B11">
         <v>15000</v>
       </c>
       <c r="C11">
@@ -1972,7 +1535,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B12">
         <v>13000</v>
@@ -1984,7 +1547,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B13">
         <v>11000</v>
@@ -1996,7 +1559,7 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="B14">
         <v>9000</v>
@@ -2041,9 +1604,9 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:E16"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="11" customWidth="1"/>
     <col min="4" max="4" width="23.28515625" customWidth="1"/>
@@ -2051,26 +1614,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
+      <c r="A1" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E3">
         <v>20</v>
@@ -2078,7 +1641,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B4">
         <v>10000</v>
@@ -2088,7 +1651,7 @@
         <v>20000</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="E4">
         <v>18</v>
@@ -2096,7 +1659,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B5">
         <v>12000</v>
@@ -2105,8 +1668,8 @@
         <f t="shared" ref="C5:C15" si="0">B5*$E$5</f>
         <v>24000</v>
       </c>
-      <c r="D5" s="7" t="s">
-        <v>19</v>
+      <c r="D5" s="6" t="s">
+        <v>23</v>
       </c>
       <c r="E5" s="3">
         <f>E3-E4</f>
@@ -2115,7 +1678,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B6">
         <v>13000</v>
@@ -2127,7 +1690,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="B7">
         <v>9000</v>
@@ -2136,13 +1699,13 @@
         <f t="shared" si="0"/>
         <v>18000</v>
       </c>
-      <c r="D7" s="4" t="s">
-        <v>21</v>
+      <c r="D7" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B8">
         <v>8000</v>
@@ -2152,7 +1715,7 @@
         <v>16000</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="E8">
         <v>200000</v>
@@ -2160,7 +1723,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B9">
         <v>11000</v>
@@ -2170,17 +1733,17 @@
         <v>22000</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E9">
         <v>250000</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A10" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10" s="6">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10">
         <v>12000</v>
       </c>
       <c r="C10">
@@ -2189,10 +1752,10 @@
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A11" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" s="6">
+      <c r="A11" t="s">
+        <v>1</v>
+      </c>
+      <c r="B11">
         <v>15000</v>
       </c>
       <c r="C11">
@@ -2200,7 +1763,7 @@
         <v>30000</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E11">
         <f>IF(B16&lt;130000,C16-E8,C16-E9)</f>
@@ -2209,7 +1772,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B12">
         <v>13000</v>
@@ -2221,7 +1784,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B13">
         <v>11000</v>
@@ -2233,7 +1796,7 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="B14">
         <v>9000</v>
@@ -2275,296 +1838,4 @@
   <pageMargins left="0.78740157499999996" right="0.78740157499999996" top="0.984251969" bottom="0.984251969" header="0.4921259845" footer="0.4921259845"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:E27"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="15.5703125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B2">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B3">
-        <v>5</v>
-      </c>
-      <c r="D3">
-        <f>ROW()-2</f>
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <f>(D3-$B$2)^2+$B$3</f>
-        <v>126</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <f t="shared" ref="D4:D27" si="0">ROW()-2</f>
-        <v>2</v>
-      </c>
-      <c r="E4">
-        <f t="shared" ref="E4:E27" si="1">(D4-$B$2)^2+$B$3</f>
-        <v>105</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B5">
-        <f>(B4-$B$2)^2+$B$3</f>
-        <v>126</v>
-      </c>
-      <c r="D5">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="E5">
-        <f t="shared" si="1"/>
-        <v>86</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="D6">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="E6">
-        <f t="shared" si="1"/>
-        <v>69</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="D7">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="E7">
-        <f t="shared" si="1"/>
-        <v>54</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="D8">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="E8">
-        <f t="shared" si="1"/>
-        <v>41</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="D9">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="E9">
-        <f t="shared" si="1"/>
-        <v>30</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="D10">
-        <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="E10">
-        <f t="shared" si="1"/>
-        <v>21</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="D11">
-        <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="E11">
-        <f t="shared" si="1"/>
-        <v>14</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="D12">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="E12">
-        <f t="shared" si="1"/>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="D13">
-        <f t="shared" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="E13">
-        <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="D14">
-        <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="E14">
-        <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="D15">
-        <f t="shared" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="E15">
-        <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="D16">
-        <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="E16">
-        <f t="shared" si="1"/>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="17" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D17">
-        <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="E17">
-        <f t="shared" si="1"/>
-        <v>14</v>
-      </c>
-    </row>
-    <row r="18" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D18">
-        <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="E18">
-        <f t="shared" si="1"/>
-        <v>21</v>
-      </c>
-    </row>
-    <row r="19" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D19">
-        <f t="shared" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="E19">
-        <f t="shared" si="1"/>
-        <v>30</v>
-      </c>
-    </row>
-    <row r="20" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D20">
-        <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="E20">
-        <f t="shared" si="1"/>
-        <v>41</v>
-      </c>
-    </row>
-    <row r="21" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D21">
-        <f t="shared" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="E21">
-        <f t="shared" si="1"/>
-        <v>54</v>
-      </c>
-    </row>
-    <row r="22" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D22">
-        <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="E22">
-        <f t="shared" si="1"/>
-        <v>69</v>
-      </c>
-    </row>
-    <row r="23" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D23">
-        <f t="shared" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="E23">
-        <f t="shared" si="1"/>
-        <v>86</v>
-      </c>
-    </row>
-    <row r="24" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D24">
-        <f t="shared" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="E24">
-        <f t="shared" si="1"/>
-        <v>105</v>
-      </c>
-    </row>
-    <row r="25" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D25">
-        <f t="shared" si="0"/>
-        <v>23</v>
-      </c>
-      <c r="E25">
-        <f t="shared" si="1"/>
-        <v>126</v>
-      </c>
-    </row>
-    <row r="26" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D26">
-        <f t="shared" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="E26">
-        <f t="shared" si="1"/>
-        <v>149</v>
-      </c>
-    </row>
-    <row r="27" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D27">
-        <f t="shared" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="E27">
-        <f t="shared" si="1"/>
-        <v>174</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.78740157499999996" right="0.78740157499999996" top="0.984251969" bottom="0.984251969" header="0.4921259845" footer="0.4921259845"/>
-  <headerFooter alignWithMargins="0"/>
-  <drawing r:id="rId1"/>
-</worksheet>
 </file>
--- a/materials/introduction_with_solutions.xlsx
+++ b/materials/introduction_with_solutions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A67147D8-0527-4183-ADD1-4ED59F0E6DFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2CCFF97-2AE0-4511-88B3-46381F6C576D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="22365" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21885" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Start" sheetId="4" r:id="rId1"/>
@@ -18,13 +18,14 @@
     <sheet name="with_plot" sheetId="1" r:id="rId3"/>
     <sheet name="simple" sheetId="6" r:id="rId4"/>
     <sheet name="conditional_cost" sheetId="5" r:id="rId5"/>
+    <sheet name="Bike_sales" sheetId="8" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="38">
   <si>
     <t>April</t>
   </si>
@@ -111,13 +112,40 @@
   </si>
   <si>
     <t>Production &gt;= 130000 =</t>
+  </si>
+  <si>
+    <t>Bike</t>
+  </si>
+  <si>
+    <t>Sales</t>
+  </si>
+  <si>
+    <t>Turnover</t>
+  </si>
+  <si>
+    <t>Cost</t>
+  </si>
+  <si>
+    <t>City-Trip</t>
+  </si>
+  <si>
+    <t>TourenCross</t>
+  </si>
+  <si>
+    <t>MTB-Downhill</t>
+  </si>
+  <si>
+    <t>MTB-SingleTrail</t>
+  </si>
+  <si>
+    <t>MTB-Monster</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -133,6 +161,14 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -142,7 +178,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -168,11 +204,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -195,6 +246,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1838,4 +1893,101 @@
   <pageMargins left="0.78740157499999996" right="0.78740157499999996" top="0.984251969" bottom="0.984251969" header="0.4921259845" footer="0.4921259845"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02E0C279-54F3-4BB6-9593-A36725325A97}">
+  <dimension ref="B2:E7"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="17.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B2" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B3" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="11">
+        <v>3</v>
+      </c>
+      <c r="D3" s="11">
+        <v>7797</v>
+      </c>
+      <c r="E3" s="11">
+        <v>4410</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B4" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" s="11">
+        <v>5</v>
+      </c>
+      <c r="D4" s="11">
+        <v>18995</v>
+      </c>
+      <c r="E4" s="11">
+        <v>12500</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B5" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C5" s="11">
+        <v>1</v>
+      </c>
+      <c r="D5" s="11">
+        <v>5799</v>
+      </c>
+      <c r="E5" s="11">
+        <v>4800</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B6" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" s="11">
+        <v>4</v>
+      </c>
+      <c r="D6" s="11">
+        <v>29996</v>
+      </c>
+      <c r="E6" s="11">
+        <v>19200</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B7" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" s="11">
+        <v>9</v>
+      </c>
+      <c r="D7" s="11">
+        <v>89910</v>
+      </c>
+      <c r="E7" s="11">
+        <v>75600</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/materials/introduction_with_solutions.xlsx
+++ b/materials/introduction_with_solutions.xlsx
@@ -1,31 +1,43 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2CCFF97-2AE0-4511-88B3-46381F6C576D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1325F2A1-C243-4138-B07C-E26BCE5B1FB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21885" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15885" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Start" sheetId="4" r:id="rId1"/>
     <sheet name="Cost_Revenue" sheetId="7" r:id="rId2"/>
-    <sheet name="with_plot" sheetId="1" r:id="rId3"/>
-    <sheet name="simple" sheetId="6" r:id="rId4"/>
-    <sheet name="conditional_cost" sheetId="5" r:id="rId5"/>
-    <sheet name="Bike_sales" sheetId="8" r:id="rId6"/>
+    <sheet name="Cost_Revenue_Painter" sheetId="9" r:id="rId3"/>
+    <sheet name="with_plot" sheetId="1" r:id="rId4"/>
+    <sheet name="simple" sheetId="6" r:id="rId5"/>
+    <sheet name="conditional_cost" sheetId="5" r:id="rId6"/>
+    <sheet name="Bike_sales" sheetId="8" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="43">
   <si>
     <t>April</t>
   </si>
@@ -139,6 +151,21 @@
   </si>
   <si>
     <t>MTB-Monster</t>
+  </si>
+  <si>
+    <t>Size (m²)</t>
+  </si>
+  <si>
+    <t>Base</t>
+  </si>
+  <si>
+    <t>Others</t>
+  </si>
+  <si>
+    <t>Patterns</t>
+  </si>
+  <si>
+    <t>Colors</t>
   </si>
 </sst>
 </file>
@@ -223,7 +250,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -240,16 +267,22 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -511,7 +544,7 @@
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="de-DE"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1"/>
@@ -566,7 +599,7 @@
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="de-DE"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="454219744"/>
@@ -609,7 +642,7 @@
           <a:cs typeface="Arial"/>
         </a:defRPr>
       </a:pPr>
-      <a:endParaRPr lang="de-DE"/>
+      <a:endParaRPr lang="en-US"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -1063,13 +1096,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
@@ -1217,6 +1250,75 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68E72385-1480-408C-BF42-C718BE1AD1D1}">
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="C1" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="C2" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="C3" s="7">
+        <v>2</v>
+      </c>
+      <c r="D3" s="7">
+        <v>4</v>
+      </c>
+      <c r="E3" s="7">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5" s="13"/>
+      <c r="B5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6" s="13"/>
+      <c r="B6">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7" s="13"/>
+      <c r="B7">
+        <v>40</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A4:A7"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F16"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
@@ -1227,13 +1329,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
       <c r="F1" s="4"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
@@ -1431,7 +1533,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:E16"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
@@ -1441,13 +1543,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
@@ -1658,7 +1760,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:E16"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
@@ -1669,13 +1771,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
@@ -1895,7 +1997,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02E0C279-54F3-4BB6-9593-A36725325A97}">
   <dimension ref="B2:E7"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
@@ -1904,86 +2006,86 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="E2" s="8" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="C3" s="11">
+      <c r="C3" s="9">
         <v>3</v>
       </c>
-      <c r="D3" s="11">
+      <c r="D3" s="9">
         <v>7797</v>
       </c>
-      <c r="E3" s="11">
+      <c r="E3" s="9">
         <v>4410</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="C4" s="11">
+      <c r="C4" s="9">
         <v>5</v>
       </c>
-      <c r="D4" s="11">
+      <c r="D4" s="9">
         <v>18995</v>
       </c>
-      <c r="E4" s="11">
+      <c r="E4" s="9">
         <v>12500</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="C5" s="11">
+      <c r="C5" s="9">
         <v>1</v>
       </c>
-      <c r="D5" s="11">
+      <c r="D5" s="9">
         <v>5799</v>
       </c>
-      <c r="E5" s="11">
+      <c r="E5" s="9">
         <v>4800</v>
       </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="11">
+      <c r="C6" s="9">
         <v>4</v>
       </c>
-      <c r="D6" s="11">
+      <c r="D6" s="9">
         <v>29996</v>
       </c>
-      <c r="E6" s="11">
+      <c r="E6" s="9">
         <v>19200</v>
       </c>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="C7" s="11">
+      <c r="C7" s="9">
         <v>9</v>
       </c>
-      <c r="D7" s="11">
+      <c r="D7" s="9">
         <v>89910</v>
       </c>
-      <c r="E7" s="11">
+      <c r="E7" s="9">
         <v>75600</v>
       </c>
     </row>
